--- a/education_forms/047_information_mind_map_form--education_forms.xlsx
+++ b/education_forms/047_information_mind_map_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Mind Map</t>
+          <t>Is this correct?</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mind Map</t>
+          <t>Select multiple options</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mind Map</t>
+          <t>Mind Map Date</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mind Map</t>
+          <t>Mind Map Time</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>mind_map_5</t>
+          <t>mind_map_4_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Mind Map</t>
+          <t>Mind Map Number</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>mind_map_6</t>
+          <t>user_input_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Mind Map</t>
+          <t>User Input 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>user_input_2</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>How do you feel?</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question_4</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>How do you see it?</t>
+          <t>What do you need?</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>question_5</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>What do you need?</t>
+          <t>How do you execute?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question_6</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How do you feel?</t>
+          <t>Is this effective?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>question_7</t>
+          <t>user_input_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>What do you need?</t>
+          <t>User Input 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>How do you feel?</t>
+          <t>How do you evaluate?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>What is the next step?</t>
+          <t>Question 9</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>How do you feel?</t>
+          <t>How do you perceive?</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What do you need?</t>
+          <t>What do you think?</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>How is it going?</t>
+          <t>What do you do?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>What do you do?</t>
+          <t>How do you adapt?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>How do you do it?</t>
+          <t>Is it a priority?</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Is it working?</t>
+          <t>What is the outcome?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>user_input_3</t>
+          <t>user_input_4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>User Input</t>
+          <t>User Input 4</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,11 +1098,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,80 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>question_7_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>question_14_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>question_14_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
